--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_41.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2520995.057303666</v>
+        <v>2514128.064355009</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900484</v>
+        <v>286.4107162900621</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900484</v>
+        <v>286.4107162900621</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>39.04534712526427</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -736,16 +736,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>119.5822865038921</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>300.9629961541974</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -894,7 +894,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>78.1807696284084</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>333.9365645502421</v>
+        <v>296.3577706585853</v>
       </c>
       <c r="S6" t="n">
         <v>385</v>
@@ -1033,7 +1033,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1091,13 +1091,13 @@
         <v>240.445564079015</v>
       </c>
       <c r="P7" t="n">
-        <v>287.4478973282775</v>
+        <v>285.8567266822216</v>
       </c>
       <c r="Q7" t="n">
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>32.46356367243068</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1216,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1261,7 +1261,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>145.3192719561528</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1270,13 +1270,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>385</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.338019733153759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>284.2120239427945</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="13">
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>144.8481678023229</v>
@@ -1726,16 +1726,16 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>259.9515598178217</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S15" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
         <v>50.21035976018675</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>279.8510241668239</v>
+        <v>283.8164155522384</v>
       </c>
       <c r="W17" t="n">
         <v>288.3734759809475</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>97.2343191717691</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>11.09991244551929</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2224,7 +2224,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>99.29663227406654</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2440,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U24" t="n">
         <v>50.21035976018675</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2632,7 +2632,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>91.60958778454074</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S27" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T27" t="n">
         <v>55.35776521751382</v>
@@ -2790,7 +2790,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D29" t="n">
         <v>60.33915573984979</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176916</v>
       </c>
       <c r="C30" t="n">
-        <v>91.60958778454074</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3078,7 +3078,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T32" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U32" t="n">
         <v>299.2212965486107</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>97.23431917176904</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
         <v>11.09991244551929</v>
@@ -3154,7 +3154,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
@@ -3264,7 +3264,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D35" t="n">
         <v>60.33915573984979</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>259.9515598178217</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3397,7 +3397,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3406,7 +3406,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3516,7 +3516,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>97.2343191717691</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3628,13 +3628,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3814,19 +3814,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>97.2343191717691</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3987,13 +3987,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H44" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,13 +4099,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429563</v>
       </c>
       <c r="U45" t="n">
         <v>50.21035976018675</v>
@@ -4303,43 +4303,43 @@
         <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="L2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>793.1</v>
       </c>
       <c r="N2" t="n">
-        <v>793.0999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="P2" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4376,16 +4376,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3619790837812</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C3" t="n">
-        <v>601.5717906960114</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D3" t="n">
-        <v>250.1195817084329</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>593.1864931608338</v>
       </c>
       <c r="F3" t="n">
         <v>250.1195817084329</v>
@@ -4421,31 +4421,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T3" t="n">
-        <v>789.9952208079459</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U3" t="n">
-        <v>789.7827362016966</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V3" t="n">
-        <v>775.1254966143025</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W3" t="n">
-        <v>742.4253522609404</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X3" t="n">
-        <v>722.3619790837812</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3619790837812</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="4">
@@ -4455,25 +4455,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1210.336612312233</v>
+        <v>1022.260933153428</v>
       </c>
       <c r="C4" t="n">
-        <v>1210.336612312233</v>
+        <v>1148.262938971864</v>
       </c>
       <c r="D4" t="n">
-        <v>1210.336612312233</v>
+        <v>1261.582083096864</v>
       </c>
       <c r="E4" t="n">
-        <v>1210.336612312233</v>
+        <v>1379.410987308277</v>
       </c>
       <c r="F4" t="n">
-        <v>1334.697584904168</v>
+        <v>1503.771959900212</v>
       </c>
       <c r="G4" t="n">
-        <v>1334.697584904168</v>
+        <v>1540</v>
       </c>
       <c r="H4" t="n">
-        <v>1334.697584904168</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="n">
         <v>1540</v>
@@ -4509,22 +4509,22 @@
         <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>218.8756791588049</v>
+        <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>465.4268717970915</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>664.2482646830374</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="W4" t="n">
-        <v>836.1391829427148</v>
+        <v>648.0635037839101</v>
       </c>
       <c r="X4" t="n">
-        <v>987.1699739669083</v>
+        <v>799.0942948081035</v>
       </c>
       <c r="Y4" t="n">
-        <v>1098.579274645941</v>
+        <v>910.5035954871358</v>
       </c>
     </row>
     <row r="5">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
         <v>62.47586368209485</v>
@@ -4558,52 +4558,52 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="L5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="N5" t="n">
-        <v>777.6999999999999</v>
+        <v>1174.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="P5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
       </c>
       <c r="R5" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>848.922759206675</v>
+        <v>712.0535963795812</v>
       </c>
       <c r="S6" t="n">
-        <v>460.0338703177861</v>
+        <v>323.1647074906923</v>
       </c>
       <c r="T6" t="n">
-        <v>454.6219862596914</v>
+        <v>317.7528234325975</v>
       </c>
       <c r="U6" t="n">
-        <v>454.4095016534421</v>
+        <v>317.5403388263483</v>
       </c>
       <c r="V6" t="n">
-        <v>439.752262066048</v>
+        <v>302.8830992389542</v>
       </c>
       <c r="W6" t="n">
-        <v>50.86337317715914</v>
+        <v>270.182954885592</v>
       </c>
       <c r="X6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>341.3787305522381</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="C7" t="n">
-        <v>467.3807363706738</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="D7" t="n">
-        <v>580.6998804956739</v>
+        <v>1249.148673865114</v>
       </c>
       <c r="E7" t="n">
-        <v>698.528784707087</v>
+        <v>1366.977578076527</v>
       </c>
       <c r="F7" t="n">
-        <v>822.8897572990224</v>
+        <v>1491.338550668462</v>
       </c>
       <c r="G7" t="n">
-        <v>976.2963231859077</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
-        <v>1145.812908345305</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1366.945787281388</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
         <v>1540</v>
@@ -4734,34 +4734,34 @@
         <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>229.621392885946</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>229.621392885946</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>229.621392885946</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>229.621392885946</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G8" t="n">
         <v>38.89056434699738</v>
@@ -4807,40 +4807,40 @@
         <v>793.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1540</v>
+        <v>1174.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1174.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
       </c>
       <c r="R8" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S8" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T8" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V8" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>720.0003429896865</v>
+        <v>30.8</v>
       </c>
       <c r="C9" t="n">
-        <v>720.0003429896865</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>720.0003429896865</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>373.8669114524009</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>789.9952208079459</v>
+        <v>823.4475019714212</v>
       </c>
       <c r="U9" t="n">
-        <v>789.7827362016966</v>
+        <v>823.2350173651719</v>
       </c>
       <c r="V9" t="n">
-        <v>775.1254966143025</v>
+        <v>808.5777777777778</v>
       </c>
       <c r="W9" t="n">
-        <v>742.4253522609404</v>
+        <v>419.6888888888889</v>
       </c>
       <c r="X9" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>720.0003429896865</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.98476868153026</v>
+        <v>142.5573376662921</v>
       </c>
       <c r="C10" t="n">
-        <v>168.986774499966</v>
+        <v>268.5593434847279</v>
       </c>
       <c r="D10" t="n">
-        <v>282.3059186249661</v>
+        <v>381.878487609728</v>
       </c>
       <c r="E10" t="n">
-        <v>400.1348228363792</v>
+        <v>499.7073918211411</v>
       </c>
       <c r="F10" t="n">
-        <v>524.4957954283146</v>
+        <v>624.0683644130766</v>
       </c>
       <c r="G10" t="n">
-        <v>677.9023613151999</v>
+        <v>777.4749302999618</v>
       </c>
       <c r="H10" t="n">
-        <v>847.4189464745974</v>
+        <v>946.9915154593593</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.55182541068</v>
+        <v>1168.124394395442</v>
       </c>
       <c r="J10" t="n">
         <v>1429.635566063132</v>
@@ -4959,22 +4959,22 @@
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
@@ -5044,13 +5044,13 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P11" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5059,25 +5059,25 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.9618669904511</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C12" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="D12" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="E12" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F12" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>913.0695679010663</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>795.3281537953983</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>739.4112192322531</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>688.6936841209533</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>623.5313940285087</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>540.3261991700961</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>469.7577754878864</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>419.8674797645184</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="13">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5272,19 +5272,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M14" t="n">
+        <v>436.0291130376558</v>
+      </c>
+      <c r="N14" t="n">
+        <v>989.4391130376557</v>
+      </c>
+      <c r="O14" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1797.400904947332</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
         <v>1797.400904947332</v>
@@ -5293,28 +5293,28 @@
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5369,13 +5369,13 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R15" t="n">
-        <v>937.5750872192207</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S15" t="n">
-        <v>819.8336731135527</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T15" t="n">
         <v>410.3813850150538</v>
@@ -5403,16 +5403,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C16" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D16" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F16" t="n">
         <v>1153.55685638681</v>
@@ -5457,22 +5457,22 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U16" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V16" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W16" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X16" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y16" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="17">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
@@ -5509,22 +5509,22 @@
         <v>44.72</v>
       </c>
       <c r="K17" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="L17" t="n">
         <v>598.13</v>
       </c>
-      <c r="L17" t="n">
-        <v>1129.18</v>
-      </c>
       <c r="M17" t="n">
-        <v>1129.18</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N17" t="n">
-        <v>1682.59</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5542,16 +5542,16 @@
         <v>1548.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5630,7 +5630,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F19" t="n">
         <v>1153.55685638681</v>
@@ -5694,22 +5694,22 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5743,25 +5743,25 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K20" t="n">
-        <v>989.4391130376558</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L20" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M20" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5846,28 +5846,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5980,52 +5980,52 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="K23" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L23" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M23" t="n">
-        <v>946.8779417665908</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N23" t="n">
-        <v>1500.287941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O23" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S23" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>407.3842417608302</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
-        <v>396.1722089875784</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6226,22 +6226,22 @@
         <v>598.13</v>
       </c>
       <c r="M26" t="n">
-        <v>690.5809049473327</v>
+        <v>598.13</v>
       </c>
       <c r="N26" t="n">
-        <v>1243.990904947333</v>
+        <v>1151.54</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>1704.95</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S26" t="n">
         <v>2085.68327354774</v>
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
         <v>44.72</v>
@@ -6320,28 +6320,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S27" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6433,22 +6433,22 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,22 +6457,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M29" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="N29" t="n">
         <v>1500.287941766591</v>
       </c>
-      <c r="N29" t="n">
-        <v>2053.697941766591</v>
-      </c>
       <c r="O29" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>472.7782575464261</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
         <v>44.72</v>
@@ -6694,16 +6694,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
         <v>1797.400904947332</v>
@@ -6721,22 +6721,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6797,25 +6797,25 @@
         <v>647.3506049216877</v>
       </c>
       <c r="S33" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T33" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U33" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V33" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W33" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X33" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y33" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="34">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
         <v>328.9211162073474</v>
@@ -6931,49 +6931,49 @@
         <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>44.72</v>
+        <v>598.13</v>
       </c>
       <c r="L35" t="n">
-        <v>598.13</v>
+        <v>1151.54</v>
       </c>
       <c r="M35" t="n">
-        <v>1108.978828728935</v>
+        <v>1151.54</v>
       </c>
       <c r="N35" t="n">
-        <v>1662.388828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="O35" t="n">
-        <v>1662.388828728935</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,13 +6983,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>937.5750872192207</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>819.8336731135527</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>763.9167385504074</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="37">
@@ -7116,19 +7116,19 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
         <v>807.7884919737335</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
         <v>44.72</v>
@@ -7168,7 +7168,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
         <v>989.4391130376558</v>
@@ -7177,13 +7177,13 @@
         <v>1500.287941766591</v>
       </c>
       <c r="N38" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7192,25 +7192,25 @@
         <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7271,25 +7271,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="40">
@@ -7414,13 +7414,13 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O41" t="n">
-        <v>2053.697941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P41" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F42" t="n">
         <v>44.72</v>
@@ -7526,7 +7526,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7536,16 +7536,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
         <v>1153.55685638681</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7630,34 +7630,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L44" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="M44" t="n">
-        <v>946.8779417665908</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N44" t="n">
-        <v>1500.287941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O44" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907174</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X45" t="n">
-        <v>204.0388125085078</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851397</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J46" t="n">
         <v>1860.696627021627</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O2" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>542.2671287719298</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>404.4874506895348</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8213,16 +8213,16 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8450,16 +8450,16 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8687,7 +8687,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>777.3630622928068</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
         <v>629.2478695740924</v>
@@ -8696,7 +8696,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,22 +8915,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>327.3708917050792</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9152,25 +9152,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>536.4141414141417</v>
-      </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>629.2478695740924</v>
+        <v>206.6237041381302</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
@@ -9395,7 +9395,7 @@
         <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>685.4145387153924</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
@@ -9407,7 +9407,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121691</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>370.3619737970638</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9869,7 +9869,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>637.6468801143706</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
         <v>1036.248958069835</v>
@@ -9878,10 +9878,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>536.7012014548231</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,7 +10100,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,13 +10112,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>254.3913627391524</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,7 +10349,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P32" t="n">
         <v>0.2870600406814136</v>
@@ -10574,25 +10574,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>1013.663099483977</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>136.6628946047192</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,25 +10811,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>559</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>777.3630622928066</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11057,16 +11057,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>497.6541815759618</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>300.4011642636528</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22949,13 +22949,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.591170646055843</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878251</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416947</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983396</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527352.5986435079</v>
+        <v>525836.742955192</v>
       </c>
       <c r="C6" t="n">
-        <v>664930.5787773224</v>
+        <v>663414.7230890061</v>
       </c>
       <c r="D6" t="n">
-        <v>666991.3506896385</v>
+        <v>665475.4950013224</v>
       </c>
       <c r="E6" t="n">
-        <v>343108.0631143748</v>
+        <v>341366.2133012674</v>
       </c>
       <c r="F6" t="n">
-        <v>686298.9584598792</v>
+        <v>684557.1086467711</v>
       </c>
       <c r="G6" t="n">
-        <v>688244.5349280646</v>
+        <v>686502.6851149572</v>
       </c>
       <c r="H6" t="n">
-        <v>690192.811745366</v>
+        <v>688450.9619322579</v>
       </c>
       <c r="I6" t="n">
-        <v>692143.8083887264</v>
+        <v>690401.9585756183</v>
       </c>
       <c r="J6" t="n">
-        <v>278577.5445903513</v>
+        <v>276835.6947772437</v>
       </c>
       <c r="K6" t="n">
-        <v>696054.0403425704</v>
+        <v>694312.1905294631</v>
       </c>
       <c r="L6" t="n">
-        <v>698013.31590283</v>
+        <v>696271.4660897225</v>
       </c>
       <c r="M6" t="n">
-        <v>638727.3917988095</v>
+        <v>636985.5419857013</v>
       </c>
       <c r="N6" t="n">
-        <v>701940.2888336629</v>
+        <v>700198.4390205549</v>
       </c>
       <c r="O6" t="n">
-        <v>423908.028091401</v>
+        <v>422166.1782782935</v>
       </c>
       <c r="P6" t="n">
-        <v>705878.630942411</v>
+        <v>704136.7811293033</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27005,7 +27005,7 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -27030,16 +27030,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -27051,13 +27051,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27439,7 +27439,7 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27515,16 +27515,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>241.5176259416272</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>41.70910106771527</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27594,25 +27594,25 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>281.6378527403057</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>384.0096324845948</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
@@ -27645,7 +27645,7 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27673,7 +27673,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>213.3372327421372</v>
+        <v>250.9160266337939</v>
       </c>
       <c r="S6" t="n">
         <v>81.5639999646113</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27843,16 +27843,16 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>294.1968519642955</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
-        <v>210.0711839052126</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
         <v>288.520773801143</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27922,7 +27922,7 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27995,10 +27995,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>260.0384932613611</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28049,13 +28049,13 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>34.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.0533730329806</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>299.4216474901395</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28089,7 +28089,7 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>299.4216474901393</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
@@ -28238,7 +28238,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
         <v>332.1680871864211</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="13">
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
         <v>350</v>
@@ -28505,16 +28505,16 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>287.3222374745576</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S15" t="n">
         <v>350</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
@@ -28551,7 +28551,7 @@
         <v>350</v>
       </c>
       <c r="F16" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G16" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28678,7 +28678,7 @@
         <v>350</v>
       </c>
       <c r="V17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="W17" t="n">
         <v>350</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28715,10 +28715,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28766,7 +28766,7 @@
         <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -28788,7 +28788,7 @@
         <v>350</v>
       </c>
       <c r="F19" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>350</v>
@@ -28946,7 +28946,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -28982,7 +28982,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -29003,7 +29003,7 @@
         <v>350</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22">
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29171,13 +29171,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="C24" t="n">
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
@@ -29219,13 +29219,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U24" t="n">
         <v>350</v>
@@ -29377,10 +29377,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29411,7 +29411,7 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29426,7 +29426,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
         <v>217.1263858913485</v>
@@ -29456,10 +29456,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T27" t="n">
         <v>350</v>
@@ -29569,7 +29569,7 @@
         <v>350</v>
       </c>
       <c r="C29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D29" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29645,10 +29645,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C30" t="n">
-        <v>269.4903246609786</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -29663,7 +29663,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29821,7 +29821,7 @@
         <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I32" t="n">
         <v>150.0811596826846</v>
@@ -29857,7 +29857,7 @@
         <v>350</v>
       </c>
       <c r="T32" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U32" t="n">
         <v>350</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="C33" t="n">
         <v>350</v>
@@ -29933,7 +29933,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T33" t="n">
         <v>350</v>
@@ -30043,7 +30043,7 @@
         <v>350</v>
       </c>
       <c r="C35" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="D35" t="n">
         <v>350</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30128,7 +30128,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30167,7 +30167,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30176,7 +30176,7 @@
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30185,7 +30185,7 @@
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30267,7 +30267,7 @@
         <v>350</v>
       </c>
       <c r="Y37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38">
@@ -30295,7 +30295,7 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30407,13 +30407,13 @@
         <v>350</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30422,7 +30422,7 @@
         <v>350</v>
       </c>
       <c r="X39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30593,19 +30593,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>274.8961667101369</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30684,7 +30684,7 @@
         <v>350</v>
       </c>
       <c r="F43" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30766,13 +30766,13 @@
         <v>350</v>
       </c>
       <c r="G44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H44" t="n">
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>269.4903246609787</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30878,13 +30878,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
       </c>
       <c r="T45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="U45" t="n">
         <v>350</v>
@@ -30933,7 +30933,7 @@
         <v>350</v>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34755,16 +34755,16 @@
         <v>385</v>
       </c>
       <c r="N2" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>385</v>
-      </c>
-      <c r="O2" t="n">
-        <v>385</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,25 +34880,25 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>36.59397989877566</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>207.3761768644765</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34931,7 +34931,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -34992,16 +34992,16 @@
         <v>385</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35129,16 +35129,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>49.15297912276548</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>174.8022350693048</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35229,16 +35229,16 @@
         <v>385</v>
       </c>
       <c r="N8" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.30784715306086</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35375,7 +35375,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>264.1526986542316</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35466,7 +35466,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>300.1141042229716</v>
+        <v>559</v>
       </c>
       <c r="O11" t="n">
         <v>559</v>
@@ -35475,7 +35475,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,22 +35694,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35837,7 +35837,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G16" t="n">
         <v>104.95612715847</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35931,25 +35931,25 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>536.4141414141417</v>
-      </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36074,7 +36074,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F19" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G19" t="n">
         <v>104.95612715847</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
@@ -36174,7 +36174,7 @@
         <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>141.1524110730751</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
@@ -36186,7 +36186,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612659</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -36417,13 +36417,13 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36648,7 +36648,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>93.38475247205321</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>559</v>
@@ -36657,10 +36657,10 @@
         <v>559</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>536.4141414141416</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,7 +36879,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>184.1434931650599</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37128,7 +37128,7 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
+        <v>559.0000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>536.4141414141413</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
       </c>
-      <c r="M35" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N35" t="n">
-        <v>559</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37553,7 +37553,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37590,25 +37590,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>559</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>300.1141042229714</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37836,16 +37836,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>559</v>
       </c>
-      <c r="O41" t="n">
-        <v>559</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
       <c r="Q41" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37970,7 +37970,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G43" t="n">
         <v>104.95612715847</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
+        <v>20.40522350612654</v>
+      </c>
+      <c r="O44" t="n">
         <v>559</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
       <c r="P44" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
